--- a/Assets/_Assets/Data/Excel/CardData.xlsx
+++ b/Assets/_Assets/Data/Excel/CardData.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="153">
   <si>
     <t xml:space="preserve">卡牌ID</t>
   </si>
@@ -470,6 +470,24 @@
   </si>
   <si>
     <t xml:space="preserve">Bank emergency cash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基础租金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目标类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseRent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">targetKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayArea</t>
   </si>
 </sst>
 </file>
@@ -1497,24 +1515,30 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1541,24 +1565,30 @@
         <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1588,13 +1618,13 @@
         <v>27</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>28</v>
@@ -1603,6 +1633,12 @@
         <v>28</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1631,19 +1667,25 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="s">
+        <v>151</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
         <v>34</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>35</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1672,19 +1714,25 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>8</v>
       </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" t="s">
         <v>39</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>34</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1713,19 +1761,25 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="s">
+        <v>151</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>4</v>
       </c>
-      <c r="J6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" t="s">
         <v>43</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>44</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1754,19 +1808,25 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="I7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" t="s">
         <v>48</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>49</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1795,19 +1855,25 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>4</v>
       </c>
-      <c r="J8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" t="s">
         <v>53</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>54</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1836,19 +1902,25 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>3</v>
       </c>
-      <c r="J9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" t="s">
         <v>58</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>39</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1877,19 +1949,25 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" t="s">
         <v>62</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>63</v>
       </c>
-      <c r="M10" t="s">
+      <c r="O10" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1918,19 +1996,25 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="s">
+        <v>151</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>6</v>
       </c>
-      <c r="J11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" t="s">
         <v>44</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>48</v>
       </c>
-      <c r="M11" t="s">
+      <c r="O11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1957,21 +2041,27 @@
         <v>60</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>6</v>
       </c>
-      <c r="J12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" t="s">
         <v>63</v>
       </c>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
         <v>53</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2000,19 +2090,25 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>3</v>
       </c>
-      <c r="J13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" t="s">
         <v>73</v>
       </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
         <v>74</v>
       </c>
-      <c r="M13" t="s">
+      <c r="O13" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2041,19 +2137,25 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>5</v>
       </c>
-      <c r="J14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" t="s">
-        <v>33</v>
-      </c>
       <c r="L14" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" t="s">
         <v>79</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2082,19 +2184,25 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="I15" t="s">
+        <v>151</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" t="s">
         <v>82</v>
       </c>
-      <c r="L15" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2123,19 +2231,25 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="s">
+        <v>151</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>8</v>
       </c>
-      <c r="J16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" t="s">
-        <v>33</v>
-      </c>
       <c r="L16" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" t="s">
         <v>85</v>
       </c>
-      <c r="M16" t="s">
+      <c r="O16" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2164,19 +2278,25 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="s">
+        <v>151</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>6</v>
       </c>
-      <c r="J17" t="s">
-        <v>33</v>
-      </c>
-      <c r="K17" t="s">
-        <v>33</v>
-      </c>
       <c r="L17" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" t="s">
         <v>88</v>
       </c>
-      <c r="M17" t="s">
+      <c r="O17" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2205,19 +2325,25 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="s">
+        <v>151</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>7</v>
       </c>
-      <c r="J18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K18" t="s">
-        <v>33</v>
-      </c>
       <c r="L18" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" t="s">
         <v>91</v>
       </c>
-      <c r="M18" t="s">
+      <c r="O18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2246,19 +2372,25 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>33</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="I19" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>33</v>
+      </c>
+      <c r="M19" t="s">
         <v>43</v>
       </c>
-      <c r="L19" t="s">
-        <v>33</v>
-      </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2287,19 +2419,25 @@
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="I20" t="s">
+        <v>152</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20" t="s">
         <v>97</v>
       </c>
-      <c r="L20" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2328,19 +2466,25 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>33</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="I21" t="s">
+        <v>152</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M21" t="s">
         <v>100</v>
       </c>
-      <c r="L21" t="s">
-        <v>33</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
+        <v>33</v>
+      </c>
+      <c r="O21" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2369,19 +2513,25 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>33</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="I22" t="s">
+        <v>152</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22" t="s">
         <v>103</v>
       </c>
-      <c r="L22" t="s">
-        <v>33</v>
-      </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2410,19 +2560,25 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>33</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="I23" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23" t="s">
         <v>106</v>
       </c>
-      <c r="L23" t="s">
-        <v>33</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
+        <v>33</v>
+      </c>
+      <c r="O23" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Assets/_Assets/Data/Excel/CardData.xlsx
+++ b/Assets/_Assets/Data/Excel/CardData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -13,8 +13,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -29,471 +29,339 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="153">
-  <si>
-    <t xml:space="preserve">卡牌ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌名称</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌说明</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌稀有度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡面插图</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花费</t>
-  </si>
-  <si>
-    <t xml:space="preserve">等待</t>
-  </si>
-  <si>
-    <t xml:space="preserve">耐久</t>
-  </si>
-  <si>
-    <t xml:space="preserve">前置效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">即时效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">结算效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">销毁效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">词条</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardArt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">waitTurns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">durability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instantEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settleEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destroyEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">打工人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">朴实的打工人，按时交租</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Tenant</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白领</t>
-  </si>
-  <si>
-    <t xml:space="preserve">写字楼白领，收入稳定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">程序员</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高薪但经常加班搬家</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">退休教师</t>
-  </si>
-  <si>
-    <t xml:space="preserve">安静的老租客，永远不走</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大学生</t>
-  </si>
-  <si>
-    <t xml:space="preserve">便宜但租期短</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">网红</t>
-  </si>
-  <si>
-    <t xml:space="preserve">出手阔绰但说走就走</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">医生</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高押金长租约</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">厨师</t>
-  </si>
-  <si>
-    <t xml:space="preserve">稳定的好租客</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">画家</t>
-  </si>
-  <si>
-    <t xml:space="preserve">需要时间安顿才开始交租</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外卖员</t>
-  </si>
-  <si>
-    <t xml:space="preserve">来得快走得也快</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">空调</t>
-  </si>
-  <si>
-    <t xml:space="preserve">提升房间舒适度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Equipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上下铺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">多住一个人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpandSlot;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">热水器</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基础设施，经久耐用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">路由器</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现代人必备</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">洗衣机</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生活便利设施</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">收房租</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一次性收取额外房租</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Event</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中介推荐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">付费获取更多候选租客</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrawCard;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">续租通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">说服所有租客续约</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddTenantDurability;3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物业维修</t>
-  </si>
-  <si>
-    <t xml:space="preserve">修缮所有设备</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddEquipmentDurability;3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紧急贷款</t>
-  </si>
-  <si>
-    <t xml:space="preserve">银行发放的应急资金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple worker, pays on time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Collar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stable income, clean room.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High pay, often overtimes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Teacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiet old tenant, never leaves.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheap but short lease.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streamer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavish pay but moves often.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High deposit, long lease.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sturdy and reliable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs time to settle in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Courier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comes fast, goes fast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air Conditioner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improves comfort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunk Bed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One more tenant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Heater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic facility, durable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WiFi Router</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life necessity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laundry convenience.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rent Bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra rent income.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent Refer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay for 2 more cards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renewal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persuade all to stay.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repair all equipment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urgent Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank emergency cash.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基础租金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目标类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseRent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">targetKind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlayArea</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="109">
+  <si>
+    <t>卡牌ID</t>
+  </si>
+  <si>
+    <t>卡牌名称</t>
+  </si>
+  <si>
+    <t>卡牌说明</t>
+  </si>
+  <si>
+    <t>卡牌类型</t>
+  </si>
+  <si>
+    <t>卡牌稀有度</t>
+  </si>
+  <si>
+    <t>卡面插图</t>
+  </si>
+  <si>
+    <t>花费</t>
+  </si>
+  <si>
+    <t>基础租金</t>
+  </si>
+  <si>
+    <t>目标类型</t>
+  </si>
+  <si>
+    <t>等待</t>
+  </si>
+  <si>
+    <t>耐久</t>
+  </si>
+  <si>
+    <t>前置效果</t>
+  </si>
+  <si>
+    <t>即时效果</t>
+  </si>
+  <si>
+    <t>结算效果</t>
+  </si>
+  <si>
+    <t>销毁效果</t>
+  </si>
+  <si>
+    <t>词条</t>
+  </si>
+  <si>
+    <t>cardId</t>
+  </si>
+  <si>
+    <t>cardName</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>cardType</t>
+  </si>
+  <si>
+    <t>rarity</t>
+  </si>
+  <si>
+    <t>cardArt</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>baseRent</t>
+  </si>
+  <si>
+    <t>targetKind</t>
+  </si>
+  <si>
+    <t>waitTurns</t>
+  </si>
+  <si>
+    <t>durability</t>
+  </si>
+  <si>
+    <t>preEffect</t>
+  </si>
+  <si>
+    <t>instantEffect</t>
+  </si>
+  <si>
+    <t>settleEffect</t>
+  </si>
+  <si>
+    <t>destroyEffect</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>Simple worker, pays on time.</t>
+  </si>
+  <si>
+    <t>Card_Tenant</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>AddMoney;60</t>
+  </si>
+  <si>
+    <t>ReduceMoney;30</t>
+  </si>
+  <si>
+    <t>White Collar</t>
+  </si>
+  <si>
+    <t>Stable income, clean room.</t>
+  </si>
+  <si>
+    <t>AddMoney;120</t>
+  </si>
+  <si>
+    <t>ReduceMoney;60</t>
+  </si>
+  <si>
+    <t>Programmer</t>
+  </si>
+  <si>
+    <t>High pay, often overtimes.</t>
+  </si>
+  <si>
+    <t>AddMoney;200</t>
+  </si>
+  <si>
+    <t>ReduceMoney;100</t>
+  </si>
+  <si>
+    <t>Senior Teacher</t>
+  </si>
+  <si>
+    <t>Quiet old tenant, never leaves.</t>
+  </si>
+  <si>
+    <t>AddMoney;50</t>
+  </si>
+  <si>
+    <t>ReduceMoney;25</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Cheap but short lease.</t>
+  </si>
+  <si>
+    <t>AddMoney;40</t>
+  </si>
+  <si>
+    <t>ReduceMoney;20</t>
+  </si>
+  <si>
+    <t>Streamer</t>
+  </si>
+  <si>
+    <t>Lavish pay but moves often.</t>
+  </si>
+  <si>
+    <t>AddMoney;240</t>
+  </si>
+  <si>
+    <t>ReduceMoney;120</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>High deposit, long lease.</t>
+  </si>
+  <si>
+    <t>AddMoney;160</t>
+  </si>
+  <si>
+    <t>ReduceMoney;80</t>
+  </si>
+  <si>
+    <t>Chef</t>
+  </si>
+  <si>
+    <t>Sturdy and reliable.</t>
+  </si>
+  <si>
+    <t>AddMoney;100</t>
+  </si>
+  <si>
+    <t>ReduceMoney;50</t>
+  </si>
+  <si>
+    <t>Painter</t>
+  </si>
+  <si>
+    <t>Needs time to settle in.</t>
+  </si>
+  <si>
+    <t>AddMoney;80</t>
+  </si>
+  <si>
+    <t>ReduceMoney;40</t>
+  </si>
+  <si>
+    <t>Courier</t>
+  </si>
+  <si>
+    <t>Comes fast, goes fast.</t>
+  </si>
+  <si>
+    <t>AddMoney;70</t>
+  </si>
+  <si>
+    <t>ReduceMoney;35</t>
+  </si>
+  <si>
+    <t>Air Conditioner</t>
+  </si>
+  <si>
+    <t>Improves comfort.</t>
+  </si>
+  <si>
+    <t>Card_Equipt</t>
+  </si>
+  <si>
+    <t>AddMoney;10</t>
+  </si>
+  <si>
+    <t>Bunk Bed</t>
+  </si>
+  <si>
+    <t>One more tenant.</t>
+  </si>
+  <si>
+    <t>ExpandSlot;1</t>
+  </si>
+  <si>
+    <t>Water Heater</t>
+  </si>
+  <si>
+    <t>Basic facility, durable.</t>
+  </si>
+  <si>
+    <t>AddMoney;5</t>
+  </si>
+  <si>
+    <t>WiFi Router</t>
+  </si>
+  <si>
+    <t>Life necessity.</t>
+  </si>
+  <si>
+    <t>AddMoney;15</t>
+  </si>
+  <si>
+    <t>Washer</t>
+  </si>
+  <si>
+    <t>Laundry convenience.</t>
+  </si>
+  <si>
+    <t>AddMoney;8</t>
+  </si>
+  <si>
+    <t>Rent Bonus</t>
+  </si>
+  <si>
+    <t>Extra rent income.</t>
+  </si>
+  <si>
+    <t>Card_Event</t>
+  </si>
+  <si>
+    <t>PlayArea</t>
+  </si>
+  <si>
+    <t>Agent Refer</t>
+  </si>
+  <si>
+    <t>Pay for 2 more cards.</t>
+  </si>
+  <si>
+    <t>DrawCard;2</t>
+  </si>
+  <si>
+    <t>Renewal</t>
+  </si>
+  <si>
+    <t>Persuade all to stay.</t>
+  </si>
+  <si>
+    <t>AddTenantDurability;3</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Repair all equipment.</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;3</t>
+  </si>
+  <si>
+    <t>Urgent Loan</t>
+  </si>
+  <si>
+    <t>Bank emergency cash.</t>
+  </si>
+  <si>
+    <t>AddMoney;500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -517,7 +385,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
@@ -525,7 +393,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
@@ -1001,155 +869,155 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1161,6 +1029,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1216,8 +1090,8 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1471,9 +1345,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.55" customWidth="1"/>
@@ -1490,9 +1364,10 @@
     <col min="12" max="12" width="22.0583333333333" customWidth="1"/>
     <col min="13" max="13" width="24.1333333333333" customWidth="1"/>
     <col min="14" max="14" width="16.4333333333333" customWidth="1"/>
+    <col min="15" max="15" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1">
+    <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1515,160 +1390,160 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1">
+    <row r="2" s="2" customFormat="1" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" s="2" customFormat="1">
+    <row r="3" s="2" customFormat="1" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1677,45 +1552,43 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" t="s">
-        <v>35</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N4"/>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>120</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1724,45 +1597,43 @@
         <v>8</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N5"/>
       <c r="O5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>200</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1771,45 +1642,43 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" t="s">
-        <v>44</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="N6"/>
       <c r="O6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>80</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1818,45 +1687,43 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="N7"/>
       <c r="O7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>30</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1865,45 +1732,43 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" t="s">
-        <v>54</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="N8"/>
       <c r="O8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G9">
         <v>150</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I9" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1912,45 +1777,43 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M9" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="N9"/>
       <c r="O9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G10">
         <v>250</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1959,45 +1822,43 @@
         <v>10</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" t="s">
         <v>63</v>
       </c>
+      <c r="N10"/>
       <c r="O10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2006,45 +1867,43 @@
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11" t="s">
-        <v>48</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N11"/>
       <c r="O11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G12">
         <v>60</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -2053,45 +1912,43 @@
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M12" t="s">
-        <v>63</v>
-      </c>
-      <c r="N12" t="s">
-        <v>53</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="N12"/>
       <c r="O12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G13">
         <v>40</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2100,36 +1957,34 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M13" t="s">
-        <v>73</v>
-      </c>
-      <c r="N13" t="s">
-        <v>74</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="N13"/>
       <c r="O13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>2001</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G14">
         <v>80</v>
@@ -2138,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2147,36 +2002,36 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>2002</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2185,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2194,36 +2049,36 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>2003</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G16">
         <v>60</v>
@@ -2232,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2241,36 +2096,36 @@
         <v>8</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>2004</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G17">
         <v>90</v>
@@ -2279,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2288,36 +2143,36 @@
         <v>6</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>2005</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G18">
         <v>70</v>
@@ -2326,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2335,36 +2190,36 @@
         <v>7</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>3001</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2373,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2382,36 +2237,36 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>3002</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G20">
         <v>50</v>
@@ -2420,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2429,36 +2284,36 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>3003</v>
       </c>
       <c r="B21" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G21">
         <v>80</v>
@@ -2467,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2476,36 +2331,36 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:15">
       <c r="A22">
         <v>3004</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G22">
         <v>60</v>
@@ -2514,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2523,36 +2378,36 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>3005</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2561,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2570,16 +2425,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2590,7 +2445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -2602,7 +2457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>

--- a/Assets/_Assets/Data/Excel/CardData.xlsx
+++ b/Assets/_Assets/Data/Excel/CardData.xlsx
@@ -1,711 +1,1096 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr autoCompressPictures="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView tabRatio="600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
-    <sheet name="CardData" sheetId="1" r:id="rId3"/>
+    <sheet name="CardData" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="223">
   <si>
-    <t xml:space="preserve">卡牌ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌名称</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌说明</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡牌稀有度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">卡面插图</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花费</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基础租金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目标类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">等待</t>
-  </si>
-  <si>
-    <t xml:space="preserve">耐久</t>
-  </si>
-  <si>
-    <t xml:space="preserve">前置效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">即时效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">结算效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">销毁效果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">词条</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cardArt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseRent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">targetKind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">waitTurns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">durability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instantEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">settleEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destroyEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple worker, pays on time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Tenant</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyRent|Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White Collar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stable income, clean room.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High pay, often overtimes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuickTurnover|Payoff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Teacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiet old tenant, never leaves.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyRent|Anchor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheap but short lease.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VacancyEconomy|Starter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streamer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavish pay but moves often.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High deposit, long lease.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sturdy and reliable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EquipmentStack|Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs time to settle in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansion|Setup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Courier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comes fast, goes fast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ReduceMoney;35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuickTurnover|Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air Conditioner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improves comfort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Equipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyRent|Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunk Bed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One more tenant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpandSlot;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansion|Engine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Heater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic facility, durable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WiFi Router</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life necessity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuickTurnover|Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laundry convenience.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rent Bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra rent income.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Event</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlayArea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BurstSettlement|Payoff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent Refer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay for 2 more cards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrawCard;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renewal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persuade all to stay.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddTenantDurability;3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repair all equipment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddEquipmentDurability;3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urgent Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank emergency cash.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Union Clerk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reliable office income with minimal churn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Night Nurse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long shifts, stable return, hard to shake.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lease Ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns each room into a cleaner revenue line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rent Reminder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A small push that keeps tenants around and the cash flowing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;60|AddTenantDurability;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SteadyRent|Tempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long Lease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locks in a low-risk income lane for several turns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card_Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;20|AddTenantDurability;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temp Worker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheap entry, quick payoff, quick exit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuickTurnover|Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Night Rider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short stay, high pace, and easy to cash out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clearance Sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keeps a busy room converting motion into cash.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recruiting Call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immediate draw to refill a fast hand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuickTurnover|Tempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relocation Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moves the lead tenant out and frees the room for the next plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoveTenantToEmptyRoom|AddMoney;20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuickTurnover|Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handyman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keeps the room's hardware alive while paying normal rent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddEquipmentDurability;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EquipmentStack|Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra Shelf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adds one more tenant slot to a built-up room.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EquipmentStack|Engine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Strip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A modest upgrade that keeps stacked devices productive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;10|AddEquipmentDurability;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laundry Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improves room comfort and keeps the tenant rolling longer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;12|AddTenantDurabilityInSelectedRoom;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EquipmentStack|Sustain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintenance Crew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repairs the building and turns upkeep into a small payout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddEquipmentDurability;3|AddMoney;40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EquipmentStack|Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subletter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low rent that converts open units into side income.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyByEmptyRooms;10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VacancyEconomy|Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open House Sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The emptier the building, the better this performs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyByEmptyRooms;15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VacancyEconomy|Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacancy Listing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cashes in on an empty unit the moment someone moves out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EvictTenantInSelectedRoom|AddMoneyByEmptyRooms;20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VacancyEconomy|Payoff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount Flyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns a quiet market into immediate card flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DrawCard;1|AddMoneyByEmptyRooms;10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VacancyEconomy|Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacancy Clause</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A contract that pays better when units stay open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyByEmptyRooms;25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VacancyEconomy|Anchor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor Planner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makes every extra room count a little more.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyByRoomCount;10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansion|Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renovation Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rewards the board for having more rooms in play.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyByRoomCount;12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partition Wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure capacity growth with no extra conditions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpandSlot;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor Permit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adds one more room and replaces itself in hand.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddRoom|DrawCard;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansion|Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blueprint Deal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A scaling contract that gets better as the property grows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyByRoomCount;20|DrawCard;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansion|Anchor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Night Auditor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pays more when the chosen room is full of tenants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyBySelectedRoomTenantCount;20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BurstSettlement|Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flash Broker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A sharp burst tenant that pays hard and leaves value behind.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyBySelectedRoomTenantCount;25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turbo Meter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns room density into one more spike every settlement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoneyBySelectedRoomTenantCount;10|AddMoney;15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BurstSettlement|Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snap Settlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triggers one safe extra settlement for the chosen room.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TriggerSelectedRoomSettle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BurstSettlement|Tempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing Statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A short contract that pushes a final money-and-cards burst.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddMoney;35|DrawCard;1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BurstSettlement|Anchor</t>
+    <t>卡牌ID</t>
+  </si>
+  <si>
+    <t>卡牌名称</t>
+  </si>
+  <si>
+    <t>卡牌说明</t>
+  </si>
+  <si>
+    <t>卡牌类型</t>
+  </si>
+  <si>
+    <t>卡牌稀有度</t>
+  </si>
+  <si>
+    <t>卡面插图</t>
+  </si>
+  <si>
+    <t>花费</t>
+  </si>
+  <si>
+    <t>基础租金</t>
+  </si>
+  <si>
+    <t>目标类型</t>
+  </si>
+  <si>
+    <t>等待</t>
+  </si>
+  <si>
+    <t>耐久</t>
+  </si>
+  <si>
+    <t>前置效果</t>
+  </si>
+  <si>
+    <t>即时效果</t>
+  </si>
+  <si>
+    <t>结算效果</t>
+  </si>
+  <si>
+    <t>销毁效果</t>
+  </si>
+  <si>
+    <t>词条</t>
+  </si>
+  <si>
+    <t>cardId</t>
+  </si>
+  <si>
+    <t>cardName</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>cardType</t>
+  </si>
+  <si>
+    <t>rarity</t>
+  </si>
+  <si>
+    <t>cardArt</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>baseRent</t>
+  </si>
+  <si>
+    <t>targetKind</t>
+  </si>
+  <si>
+    <t>waitTurns</t>
+  </si>
+  <si>
+    <t>durability</t>
+  </si>
+  <si>
+    <t>preEffect</t>
+  </si>
+  <si>
+    <t>instantEffect</t>
+  </si>
+  <si>
+    <t>settleEffect</t>
+  </si>
+  <si>
+    <t>destroyEffect</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>工人</t>
+  </si>
+  <si>
+    <t>勤快的工人，准时交租。</t>
+  </si>
+  <si>
+    <t>Card_Tenant</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>AddMoney;60</t>
+  </si>
+  <si>
+    <t>ReduceMoney;30</t>
+  </si>
+  <si>
+    <t>SteadyRent|Core</t>
+  </si>
+  <si>
+    <t>白领</t>
+  </si>
+  <si>
+    <t>工作稳定，房间整洁。</t>
+  </si>
+  <si>
+    <t>AddMoney;120</t>
+  </si>
+  <si>
+    <t>ReduceMoney;60</t>
+  </si>
+  <si>
+    <t>程序员</t>
+  </si>
+  <si>
+    <t>高薪但经常加班。</t>
+  </si>
+  <si>
+    <t>AddMoney;200</t>
+  </si>
+  <si>
+    <t>ReduceMoney;100</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Payoff</t>
+  </si>
+  <si>
+    <t>高级教师</t>
+  </si>
+  <si>
+    <t>安静的老房客，长住不走。</t>
+  </si>
+  <si>
+    <t>AddMoney;50</t>
+  </si>
+  <si>
+    <t>ReduceMoney;25</t>
+  </si>
+  <si>
+    <t>SteadyRent|Anchor</t>
+  </si>
+  <si>
+    <t>学生</t>
+  </si>
+  <si>
+    <t>房租便宜但租期短。</t>
+  </si>
+  <si>
+    <t>AddMoney;40</t>
+  </si>
+  <si>
+    <t>ReduceMoney;20</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Starter</t>
+  </si>
+  <si>
+    <t>主播</t>
+  </si>
+  <si>
+    <t>高收入但经常搬家。</t>
+  </si>
+  <si>
+    <t>AddMoney;240</t>
+  </si>
+  <si>
+    <t>ReduceMoney;120</t>
+  </si>
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>定金高，长期承租。</t>
+  </si>
+  <si>
+    <t>AddMoney;160</t>
+  </si>
+  <si>
+    <t>ReduceMoney;80</t>
+  </si>
+  <si>
+    <t>厨师</t>
+  </si>
+  <si>
+    <t>稳定可靠的好房客。</t>
+  </si>
+  <si>
+    <t>AddMoney;100</t>
+  </si>
+  <si>
+    <t>ReduceMoney;50</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Support</t>
+  </si>
+  <si>
+    <t>画家</t>
+  </si>
+  <si>
+    <t>需要时间适应新房间。</t>
+  </si>
+  <si>
+    <t>AddMoney;80</t>
+  </si>
+  <si>
+    <t>ReduceMoney;40</t>
+  </si>
+  <si>
+    <t>Expansion|Setup</t>
+  </si>
+  <si>
+    <t>快递员</t>
+  </si>
+  <si>
+    <t>来得快，去得也快。</t>
+  </si>
+  <si>
+    <t>AddMoney;70</t>
+  </si>
+  <si>
+    <t>ReduceMoney;35</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Bridge</t>
+  </si>
+  <si>
+    <t>空调</t>
+  </si>
+  <si>
+    <t>提升房间舒适度。</t>
+  </si>
+  <si>
+    <t>Card_Equipt</t>
+  </si>
+  <si>
+    <t>AddMoney;10</t>
+  </si>
+  <si>
+    <t>SteadyRent|Support</t>
+  </si>
+  <si>
+    <t>双层床</t>
+  </si>
+  <si>
+    <t>增加一个房客位置。</t>
+  </si>
+  <si>
+    <t>ExpandSlot;1</t>
+  </si>
+  <si>
+    <t>Expansion|Engine</t>
+  </si>
+  <si>
+    <t>热水器</t>
+  </si>
+  <si>
+    <t>基础设施，耐用性强。</t>
+  </si>
+  <si>
+    <t>AddMoney;5</t>
+  </si>
+  <si>
+    <t>WiFi路由器</t>
+  </si>
+  <si>
+    <t>生活必需品。</t>
+  </si>
+  <si>
+    <t>AddMoney;15</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Support</t>
+  </si>
+  <si>
+    <t>洗衣机</t>
+  </si>
+  <si>
+    <t>洗衣便利性。</t>
+  </si>
+  <si>
+    <t>AddMoney;8</t>
+  </si>
+  <si>
+    <t>租金奖励</t>
+  </si>
+  <si>
+    <t>额外的租金收入。</t>
+  </si>
+  <si>
+    <t>Card_Event</t>
+  </si>
+  <si>
+    <t>PlayArea</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Payoff</t>
+  </si>
+  <si>
+    <t>经纪人介绍</t>
+  </si>
+  <si>
+    <t>支付费用抽取2张牌。</t>
+  </si>
+  <si>
+    <t>DrawCard;2</t>
+  </si>
+  <si>
+    <t>续签</t>
+  </si>
+  <si>
+    <t>说服所有房客留下。</t>
+  </si>
+  <si>
+    <t>AddTenantDurability;3</t>
+  </si>
+  <si>
+    <t>维修</t>
+  </si>
+  <si>
+    <t>修复所有设备。</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;3</t>
+  </si>
+  <si>
+    <t>应急贷款</t>
+  </si>
+  <si>
+    <t>银行紧急资金。</t>
+  </si>
+  <si>
+    <t>AddMoney;500</t>
+  </si>
+  <si>
+    <t>工会文员</t>
+  </si>
+  <si>
+    <t>可靠的办公收入，房客流失少。</t>
+  </si>
+  <si>
+    <t>夜班护士</t>
+  </si>
+  <si>
+    <t>长班次，稳定回报，难以驱赶。</t>
+  </si>
+  <si>
+    <t>租赁账本</t>
+  </si>
+  <si>
+    <t>把每个房间变成更清洁的收益线。</t>
+  </si>
+  <si>
+    <t>催租单</t>
+  </si>
+  <si>
+    <t>小小推动让房客继续交租和现金流动。</t>
+  </si>
+  <si>
+    <t>AddMoney;60|AddTenantDurability;2</t>
+  </si>
+  <si>
+    <t>SteadyRent|Tempo</t>
+  </si>
+  <si>
+    <t>长期租约</t>
+  </si>
+  <si>
+    <t>在多个回合内锁定低风险收入。</t>
+  </si>
+  <si>
+    <t>Card_Contract</t>
+  </si>
+  <si>
+    <t>AddMoney;20|AddTenantDurability;1</t>
+  </si>
+  <si>
+    <t>临时工</t>
+  </si>
+  <si>
+    <t>便宜入场，快速回报，快速退出。</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Core</t>
+  </si>
+  <si>
+    <t>夜骑手</t>
+  </si>
+  <si>
+    <t>短期入住，高速节奏，容易变现。</t>
+  </si>
+  <si>
+    <t>清仓招牌</t>
+  </si>
+  <si>
+    <t>让繁忙房间持续转化为现金。</t>
+  </si>
+  <si>
+    <t>招聘电话</t>
+  </si>
+  <si>
+    <t>立即抽牌补充手牌。</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Tempo</t>
+  </si>
+  <si>
+    <t>搬迁令</t>
+  </si>
+  <si>
+    <t>让头号房客搬出，为下一步计划腾出房间。</t>
+  </si>
+  <si>
+    <t>MoveTenantToEmptyRoom|AddMoney;20</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Control</t>
+  </si>
+  <si>
+    <t>万能工</t>
+  </si>
+  <si>
+    <t>保持房间硬件完好，照常交租。</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;1</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Core</t>
+  </si>
+  <si>
+    <t>额外书架</t>
+  </si>
+  <si>
+    <t>为堆满的房间增加一个房客位置。</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Engine</t>
+  </si>
+  <si>
+    <t>电源插座</t>
+  </si>
+  <si>
+    <t>温和升级让叠放设备保持高效。</t>
+  </si>
+  <si>
+    <t>AddMoney;10|AddEquipmentDurability;1</t>
+  </si>
+  <si>
+    <t>洗衣堆</t>
+  </si>
+  <si>
+    <t>提升房间舒适度，房客留存更久。</t>
+  </si>
+  <si>
+    <t>AddMoney;12|AddTenantDurabilityInSelectedRoom;1</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Sustain</t>
+  </si>
+  <si>
+    <t>维修队</t>
+  </si>
+  <si>
+    <t>修复建筑并把维护费转化为小额收益。</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;3|AddMoney;40</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Bridge</t>
+  </si>
+  <si>
+    <t>转租户</t>
+  </si>
+  <si>
+    <t>低租金把闲置单位变成额外收入。</t>
+  </si>
+  <si>
+    <t>AddMoneyByEmptyRooms;10</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Core</t>
+  </si>
+  <si>
+    <t>开放屋标志</t>
+  </si>
+  <si>
+    <t>房屋越空，表现越好。</t>
+  </si>
+  <si>
+    <t>AddMoneyByEmptyRooms;15</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Support</t>
+  </si>
+  <si>
+    <t>空房清单</t>
+  </si>
+  <si>
+    <t>有人搬出时立即从空单位变现。</t>
+  </si>
+  <si>
+    <t>EvictTenantInSelectedRoom|AddMoneyByEmptyRooms;20</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Payoff</t>
+  </si>
+  <si>
+    <t>折扣传单</t>
+  </si>
+  <si>
+    <t>把冷淡市场变成立即抽牌。</t>
+  </si>
+  <si>
+    <t>DrawCard;1|AddMoneyByEmptyRooms;10</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Bridge</t>
+  </si>
+  <si>
+    <t>空房条款</t>
+  </si>
+  <si>
+    <t>单位保持空房时付款更高。</t>
+  </si>
+  <si>
+    <t>AddMoneyByEmptyRooms;25</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Anchor</t>
+  </si>
+  <si>
+    <t>楼层规划师</t>
+  </si>
+  <si>
+    <t>每增加一个房间就赚一点。</t>
+  </si>
+  <si>
+    <t>AddMoneyByRoomCount;10</t>
+  </si>
+  <si>
+    <t>Expansion|Core</t>
+  </si>
+  <si>
+    <t>装修负责人</t>
+  </si>
+  <si>
+    <t>建筑有更多房间在用时获得奖励。</t>
+  </si>
+  <si>
+    <t>AddMoneyByRoomCount;12</t>
+  </si>
+  <si>
+    <t>隔断墙</t>
+  </si>
+  <si>
+    <t>纯容量增长，无额外条件。</t>
+  </si>
+  <si>
+    <t>ExpandSlot;2</t>
+  </si>
+  <si>
+    <t>施工许可</t>
+  </si>
+  <si>
+    <t>增加一个房间并在手牌中替换自己。</t>
+  </si>
+  <si>
+    <t>AddRoom|DrawCard;1</t>
+  </si>
+  <si>
+    <t>Expansion|Bridge</t>
+  </si>
+  <si>
+    <t>蓝图交易</t>
+  </si>
+  <si>
+    <t>随着地产增长而变得更好的可扩展合约。</t>
+  </si>
+  <si>
+    <t>AddMoneyByRoomCount;20|DrawCard;1</t>
+  </si>
+  <si>
+    <t>Expansion|Anchor</t>
+  </si>
+  <si>
+    <t>夜间审计员</t>
+  </si>
+  <si>
+    <t>选中的房间满客时支付更多。</t>
+  </si>
+  <si>
+    <t>AddMoneyBySelectedRoomTenantCount;20</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Core</t>
+  </si>
+  <si>
+    <t>闪电经纪人</t>
+  </si>
+  <si>
+    <t>短期高薪房客，留下增值残余。</t>
+  </si>
+  <si>
+    <t>AddMoneyBySelectedRoomTenantCount;25</t>
+  </si>
+  <si>
+    <t>涡轮计价表</t>
+  </si>
+  <si>
+    <t>把房间密度转化为每次结算的额外冲刺。</t>
+  </si>
+  <si>
+    <t>AddMoneyBySelectedRoomTenantCount;10|AddMoney;15</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Support</t>
+  </si>
+  <si>
+    <t>快速结算</t>
+  </si>
+  <si>
+    <t>为选中的房间触发一次安全的额外结算。</t>
+  </si>
+  <si>
+    <t>TriggerSelectedRoomSettle</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Tempo</t>
+  </si>
+  <si>
+    <t>最终对账</t>
+  </si>
+  <si>
+    <t>短期合约推动最后的现金和牌张突发。</t>
+  </si>
+  <si>
+    <t>AddMoney;35|DrawCard;1</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Anchor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -713,190 +1098,1012 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="55.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="51.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="51.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="17.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="23.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="7.425" customWidth="1"/>
+    <col min="2" max="2" width="17.1416666666667" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="13.425" customWidth="1"/>
+    <col min="5" max="5" width="12.5666666666667" customWidth="1"/>
+    <col min="6" max="6" width="10.2833333333333" customWidth="1"/>
+    <col min="7" max="7" width="5.70833333333333" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="10" width="14.375" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="51.425" customWidth="1"/>
+    <col min="14" max="14" width="51.7083333333333" customWidth="1"/>
+    <col min="15" max="15" width="17.1416666666667" customWidth="1"/>
+    <col min="16" max="16" width="23.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:16">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:16">
+      <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:16">
+      <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -946,7 +2153,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>1002</v>
       </c>
@@ -996,7 +2203,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>1003</v>
       </c>
@@ -1046,7 +2253,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>1004</v>
       </c>
@@ -1096,7 +2303,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>1005</v>
       </c>
@@ -1146,7 +2353,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>1006</v>
       </c>
@@ -1196,7 +2403,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>1007</v>
       </c>
@@ -1246,7 +2453,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>1008</v>
       </c>
@@ -1296,7 +2503,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>1009</v>
       </c>
@@ -1346,7 +2553,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>1010</v>
       </c>
@@ -1396,7 +2603,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>2001</v>
       </c>
@@ -1446,7 +2653,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>2002</v>
       </c>
@@ -1496,7 +2703,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>2003</v>
       </c>
@@ -1546,7 +2753,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>2004</v>
       </c>
@@ -1596,7 +2803,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>2005</v>
       </c>
@@ -1646,7 +2853,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>3001</v>
       </c>
@@ -1696,7 +2903,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>3002</v>
       </c>
@@ -1746,7 +2953,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>3003</v>
       </c>
@@ -1796,7 +3003,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>3004</v>
       </c>
@@ -1846,7 +3053,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>3005</v>
       </c>
@@ -1896,7 +3103,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>1011</v>
       </c>
@@ -1946,7 +3153,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>1012</v>
       </c>
@@ -1996,7 +3203,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>2006</v>
       </c>
@@ -2046,7 +3253,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>3006</v>
       </c>
@@ -2096,7 +3303,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>4001</v>
       </c>
@@ -2146,7 +3353,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>1013</v>
       </c>
@@ -2196,7 +3403,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>1014</v>
       </c>
@@ -2246,7 +3453,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>2007</v>
       </c>
@@ -2296,7 +3503,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>3007</v>
       </c>
@@ -2346,7 +3553,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>3008</v>
       </c>
@@ -2396,7 +3603,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>1015</v>
       </c>
@@ -2446,7 +3653,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>2008</v>
       </c>
@@ -2496,7 +3703,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>2009</v>
       </c>
@@ -2546,7 +3753,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>2010</v>
       </c>
@@ -2596,7 +3803,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>3009</v>
       </c>
@@ -2646,7 +3853,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>1016</v>
       </c>
@@ -2696,7 +3903,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>2011</v>
       </c>
@@ -2746,7 +3953,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>3010</v>
       </c>
@@ -2796,7 +4003,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>3011</v>
       </c>
@@ -2846,7 +4053,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>4002</v>
       </c>
@@ -2896,7 +4103,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>1017</v>
       </c>
@@ -2946,7 +4153,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>1018</v>
       </c>
@@ -2996,7 +4203,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>2012</v>
       </c>
@@ -3046,7 +4253,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>3012</v>
       </c>
@@ -3096,7 +4303,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>4003</v>
       </c>
@@ -3146,7 +4353,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>1019</v>
       </c>
@@ -3196,7 +4403,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>1020</v>
       </c>
@@ -3246,7 +4453,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>2013</v>
       </c>
@@ -3296,7 +4503,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:16">
       <c r="A52">
         <v>3013</v>
       </c>
@@ -3346,7 +4553,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:16">
       <c r="A53">
         <v>4004</v>
       </c>
@@ -3398,5 +4605,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/_Assets/Data/Excel/CardData.xlsx
+++ b/Assets/_Assets/Data/Excel/CardData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="225">
   <si>
     <t>卡牌ID</t>
   </si>
@@ -77,6 +77,9 @@
     <t>词条</t>
   </si>
   <si>
+    <t>牌库</t>
+  </si>
+  <si>
     <t>cardId</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>destroyEffect</t>
+  </si>
+  <si>
+    <t>libraries</t>
   </si>
   <si>
     <t>int</t>
@@ -1359,7 +1365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1367,12 +1373,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1933,7 +1934,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.425" customWidth="1"/>
@@ -1951,176 +1952,186 @@
     <col min="14" max="14" width="51.7083333333333" customWidth="1"/>
     <col min="15" max="15" width="17.1416666666667" customWidth="1"/>
     <col min="16" max="16" width="23.7083333333333" customWidth="1"/>
+    <col min="17" max="17" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:17">
+      <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="L2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="M2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:16">
-      <c r="A3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="Q2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:17">
+      <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="F3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -2129,7 +2140,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2138,39 +2149,42 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5">
         <v>120</v>
@@ -2179,7 +2193,7 @@
         <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2188,39 +2202,42 @@
         <v>8</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>200</v>
@@ -2229,7 +2246,7 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2238,39 +2255,42 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G7">
         <v>80</v>
@@ -2279,7 +2299,7 @@
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2288,39 +2308,42 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>57</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G8">
         <v>30</v>
@@ -2329,7 +2352,7 @@
         <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2338,39 +2361,42 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>62</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9">
         <v>150</v>
@@ -2379,7 +2405,7 @@
         <v>120</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2388,39 +2414,42 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>250</v>
@@ -2429,7 +2458,7 @@
         <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2438,39 +2467,42 @@
         <v>10</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -2479,7 +2511,7 @@
         <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2488,39 +2520,42 @@
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>75</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G12">
         <v>60</v>
@@ -2529,7 +2564,7 @@
         <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -2538,39 +2573,42 @@
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>80</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13">
         <v>40</v>
@@ -2579,7 +2617,7 @@
         <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2588,39 +2626,42 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>85</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>2001</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G14">
         <v>80</v>
@@ -2629,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2638,39 +2679,42 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>90</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>2002</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2679,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2688,39 +2732,42 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>94</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>2003</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16">
         <v>60</v>
@@ -2729,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2738,39 +2785,42 @@
         <v>8</v>
       </c>
       <c r="L16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>90</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17">
         <v>2004</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17">
         <v>90</v>
@@ -2779,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2788,39 +2838,42 @@
         <v>6</v>
       </c>
       <c r="L17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>101</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>2005</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G18">
         <v>70</v>
@@ -2829,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2838,39 +2891,42 @@
         <v>7</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>75</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19">
         <v>3001</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2879,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2888,39 +2944,42 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P19" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>109</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20">
         <v>3002</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G20">
         <v>50</v>
@@ -2929,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2938,39 +2997,42 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>85</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21">
         <v>3003</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G21">
         <v>80</v>
@@ -2979,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2988,39 +3050,42 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>90</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22">
         <v>3004</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G22">
         <v>60</v>
@@ -3029,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3038,39 +3103,42 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+        <v>75</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23">
         <v>3005</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3079,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3088,39 +3156,42 @@
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P23" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>109</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24">
         <v>1011</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G24">
         <v>70</v>
@@ -3129,7 +3200,7 @@
         <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3138,39 +3209,42 @@
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>43</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25">
         <v>1012</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G25">
         <v>95</v>
@@ -3179,7 +3253,7 @@
         <v>45</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3188,39 +3262,42 @@
         <v>7</v>
       </c>
       <c r="L25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+        <v>43</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26">
         <v>2006</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G26">
         <v>85</v>
@@ -3229,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3238,39 +3315,42 @@
         <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>90</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27">
         <v>3006</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G27">
         <v>40</v>
@@ -3279,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3288,39 +3368,42 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P27" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+        <v>131</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28">
         <v>4001</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G28">
         <v>120</v>
@@ -3329,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3338,39 +3421,42 @@
         <v>4</v>
       </c>
       <c r="L28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+        <v>57</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29">
         <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G29">
         <v>55</v>
@@ -3379,7 +3465,7 @@
         <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3388,39 +3474,42 @@
         <v>4</v>
       </c>
       <c r="L29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>138</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30">
         <v>1014</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G30">
         <v>80</v>
@@ -3429,7 +3518,7 @@
         <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3438,39 +3527,42 @@
         <v>3</v>
       </c>
       <c r="L30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>52</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31">
         <v>2007</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G31">
         <v>65</v>
@@ -3479,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -3488,39 +3580,42 @@
         <v>4</v>
       </c>
       <c r="L31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+        <v>101</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32">
         <v>3007</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G32">
         <v>40</v>
@@ -3529,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -3538,39 +3633,42 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P32" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
+        <v>145</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33">
         <v>3008</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G33">
         <v>25</v>
@@ -3579,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -3588,39 +3686,42 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P33" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+        <v>149</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34">
         <v>1015</v>
       </c>
       <c r="B34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G34">
         <v>60</v>
@@ -3629,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -3638,39 +3739,42 @@
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+        <v>153</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35">
         <v>2008</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G35">
         <v>80</v>
@@ -3679,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -3688,39 +3792,42 @@
         <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P35" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
+        <v>156</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36">
         <v>2009</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G36">
         <v>70</v>
@@ -3729,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -3738,39 +3845,42 @@
         <v>5</v>
       </c>
       <c r="L36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+        <v>75</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37">
         <v>2010</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G37">
         <v>95</v>
@@ -3779,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -3788,39 +3898,42 @@
         <v>6</v>
       </c>
       <c r="L37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+        <v>163</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38">
         <v>3009</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G38">
         <v>55</v>
@@ -3829,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -3838,39 +3951,42 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P38" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+        <v>167</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39">
         <v>1016</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G39">
         <v>45</v>
@@ -3879,7 +3995,7 @@
         <v>20</v>
       </c>
       <c r="I39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -3888,39 +4004,42 @@
         <v>4</v>
       </c>
       <c r="L39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P39" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+        <v>171</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40">
         <v>2011</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G40">
         <v>70</v>
@@ -3929,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -3938,39 +4057,42 @@
         <v>4</v>
       </c>
       <c r="L40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P40" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+        <v>175</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
       <c r="A41">
         <v>3010</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D41" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G41">
         <v>20</v>
@@ -3979,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3988,39 +4110,42 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M41" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
+        <v>179</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
       <c r="A42">
         <v>3011</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D42" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4029,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -4038,39 +4163,42 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
+        <v>183</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
       <c r="A43">
         <v>4002</v>
       </c>
       <c r="B43" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -4079,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -4088,39 +4216,42 @@
         <v>4</v>
       </c>
       <c r="L43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
+        <v>187</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
       <c r="A44">
         <v>1017</v>
       </c>
       <c r="B44" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G44">
         <v>65</v>
@@ -4129,7 +4260,7 @@
         <v>28</v>
       </c>
       <c r="I44" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -4138,39 +4269,42 @@
         <v>5</v>
       </c>
       <c r="L44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N44" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
+        <v>191</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45">
         <v>1018</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E45">
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G45">
         <v>70</v>
@@ -4179,7 +4313,7 @@
         <v>32</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -4188,39 +4322,42 @@
         <v>5</v>
       </c>
       <c r="L45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N45" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
+        <v>191</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46">
         <v>2012</v>
       </c>
       <c r="B46" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C46" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E46">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G46">
         <v>110</v>
@@ -4229,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -4238,39 +4375,42 @@
         <v>5</v>
       </c>
       <c r="L46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P46" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
+        <v>94</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47">
         <v>3012</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C47" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D47" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G47">
         <v>80</v>
@@ -4279,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -4288,39 +4428,42 @@
         <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M47" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
+        <v>201</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48">
         <v>4003</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G48">
         <v>140</v>
@@ -4329,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -4338,39 +4481,42 @@
         <v>4</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M48" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N48" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O48" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P48" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
+        <v>205</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49">
         <v>1019</v>
       </c>
       <c r="B49" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G49">
         <v>50</v>
@@ -4379,7 +4525,7 @@
         <v>20</v>
       </c>
       <c r="I49" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -4388,39 +4534,42 @@
         <v>4</v>
       </c>
       <c r="L49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N49" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P49" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
+        <v>209</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17">
       <c r="A50">
         <v>1020</v>
       </c>
       <c r="B50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E50">
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G50">
         <v>80</v>
@@ -4429,7 +4578,7 @@
         <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -4438,39 +4587,42 @@
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O50" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P50" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16">
+        <v>109</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
       <c r="A51">
         <v>2013</v>
       </c>
       <c r="B51" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E51">
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G51">
         <v>90</v>
@@ -4479,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -4488,39 +4640,42 @@
         <v>4</v>
       </c>
       <c r="L51" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M51" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O51" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P51" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16">
+        <v>216</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
       <c r="A52">
         <v>3013</v>
       </c>
       <c r="B52" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G52">
         <v>70</v>
@@ -4529,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -4538,39 +4693,42 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M52" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
+        <v>220</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
       <c r="A53">
         <v>4004</v>
       </c>
       <c r="B53" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C53" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E53">
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G53">
         <v>130</v>
@@ -4579,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -4588,19 +4746,22 @@
         <v>3</v>
       </c>
       <c r="L53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P53" t="s">
-        <v>222</v>
+        <v>224</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/_Assets/Data/Excel/CardData.xlsx
+++ b/Assets/_Assets/Data/Excel/CardData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="228">
   <si>
     <t>卡牌ID</t>
   </si>
@@ -137,70 +137,487 @@
     <t>enum</t>
   </si>
   <si>
+    <t>程序员</t>
+  </si>
+  <si>
+    <t>高薪但经常加班。</t>
+  </si>
+  <si>
+    <t>Card_Tenant</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>AddMoney;200</t>
+  </si>
+  <si>
+    <t>ReduceMoney;100</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Payoff</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>主播</t>
+  </si>
+  <si>
+    <t>高收入但经常搬家。</t>
+  </si>
+  <si>
+    <t>AddMoney;240</t>
+  </si>
+  <si>
+    <t>ReduceMoney;120</t>
+  </si>
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>定金高，长期承租。</t>
+  </si>
+  <si>
+    <t>AddMoney;160</t>
+  </si>
+  <si>
+    <t>ReduceMoney;80</t>
+  </si>
+  <si>
+    <t>SteadyRent|Core</t>
+  </si>
+  <si>
+    <t>双层床</t>
+  </si>
+  <si>
+    <t>增加一个房客位置。</t>
+  </si>
+  <si>
+    <t>Card_Equipt</t>
+  </si>
+  <si>
+    <t>ExpandSlot;1</t>
+  </si>
+  <si>
+    <t>Expansion|Engine</t>
+  </si>
+  <si>
+    <t>应急贷款</t>
+  </si>
+  <si>
+    <t>银行紧急资金。</t>
+  </si>
+  <si>
+    <t>Card_Event</t>
+  </si>
+  <si>
+    <t>PlayArea</t>
+  </si>
+  <si>
+    <t>AddMoney;500</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Payoff</t>
+  </si>
+  <si>
+    <t>夜班护士</t>
+  </si>
+  <si>
+    <t>长班次，稳定回报，难以驱赶。</t>
+  </si>
+  <si>
+    <t>ReduceMoney;30</t>
+  </si>
+  <si>
+    <t>洗衣堆</t>
+  </si>
+  <si>
+    <t>提升房间舒适度，房客留存更久。</t>
+  </si>
+  <si>
+    <t>AddMoney;12|AddTenantDurabilityInSelectedRoom;1</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Sustain</t>
+  </si>
+  <si>
+    <t>装修负责人</t>
+  </si>
+  <si>
+    <t>建筑有更多房间在用时获得奖励。</t>
+  </si>
+  <si>
+    <t>AddMoneyByRoomCount;12</t>
+  </si>
+  <si>
+    <t>Expansion|Core</t>
+  </si>
+  <si>
+    <t>隔断墙</t>
+  </si>
+  <si>
+    <t>纯容量增长，无额外条件。</t>
+  </si>
+  <si>
+    <t>ExpandSlot;2</t>
+  </si>
+  <si>
+    <t>蓝图交易</t>
+  </si>
+  <si>
+    <t>随着地产增长而变得更好的可扩展合约。</t>
+  </si>
+  <si>
+    <t>Card_Contract</t>
+  </si>
+  <si>
+    <t>AddMoneyByRoomCount;20|DrawCard;1</t>
+  </si>
+  <si>
+    <t>Expansion|Anchor</t>
+  </si>
+  <si>
+    <t>闪电经纪人</t>
+  </si>
+  <si>
+    <t>短期高薪房客，留下增值残余。</t>
+  </si>
+  <si>
+    <t>AddMoneyBySelectedRoomTenantCount;25</t>
+  </si>
+  <si>
+    <t>AddMoney;70</t>
+  </si>
+  <si>
+    <t>涡轮计价表</t>
+  </si>
+  <si>
+    <t>把房间密度转化为每次结算的额外冲刺。</t>
+  </si>
+  <si>
+    <t>AddMoneyBySelectedRoomTenantCount;10|AddMoney;15</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Support</t>
+  </si>
+  <si>
+    <t>最终对账</t>
+  </si>
+  <si>
+    <t>短期合约推动最后的现金和牌张突发。</t>
+  </si>
+  <si>
+    <t>AddMoney;35|DrawCard;1</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Anchor</t>
+  </si>
+  <si>
+    <t>白领</t>
+  </si>
+  <si>
+    <t>工作稳定，房间整洁。</t>
+  </si>
+  <si>
+    <t>AddMoney;120</t>
+  </si>
+  <si>
+    <t>ReduceMoney;60</t>
+  </si>
+  <si>
+    <t>0|1|2</t>
+  </si>
+  <si>
+    <t>高级教师</t>
+  </si>
+  <si>
+    <t>安静的老房客，长住不走。</t>
+  </si>
+  <si>
+    <t>AddMoney;50</t>
+  </si>
+  <si>
+    <t>ReduceMoney;25</t>
+  </si>
+  <si>
+    <t>SteadyRent|Anchor</t>
+  </si>
+  <si>
+    <t>厨师</t>
+  </si>
+  <si>
+    <t>稳定可靠的好房客。</t>
+  </si>
+  <si>
+    <t>AddMoney;100</t>
+  </si>
+  <si>
+    <t>ReduceMoney;50</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Support</t>
+  </si>
+  <si>
+    <t>画家</t>
+  </si>
+  <si>
+    <t>需要时间适应新房间。</t>
+  </si>
+  <si>
+    <t>AddMoney;80</t>
+  </si>
+  <si>
+    <t>ReduceMoney;40</t>
+  </si>
+  <si>
+    <t>Expansion|Setup</t>
+  </si>
+  <si>
+    <t>空调</t>
+  </si>
+  <si>
+    <t>提升房间舒适度。</t>
+  </si>
+  <si>
+    <t>AddMoney;10</t>
+  </si>
+  <si>
+    <t>SteadyRent|Support</t>
+  </si>
+  <si>
+    <t>WiFi路由器</t>
+  </si>
+  <si>
+    <t>生活必需品。</t>
+  </si>
+  <si>
+    <t>AddMoney;15</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Support</t>
+  </si>
+  <si>
+    <t>洗衣机</t>
+  </si>
+  <si>
+    <t>洗衣便利性。</t>
+  </si>
+  <si>
+    <t>AddMoney;8</t>
+  </si>
+  <si>
+    <t>经纪人介绍</t>
+  </si>
+  <si>
+    <t>支付费用抽取2张牌。</t>
+  </si>
+  <si>
+    <t>DrawCard;2</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Bridge</t>
+  </si>
+  <si>
+    <t>续签</t>
+  </si>
+  <si>
+    <t>说服所有房客留下。</t>
+  </si>
+  <si>
+    <t>AddTenantDurability;3</t>
+  </si>
+  <si>
+    <t>维修</t>
+  </si>
+  <si>
+    <t>修复所有设备。</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;3</t>
+  </si>
+  <si>
+    <t>工会文员</t>
+  </si>
+  <si>
+    <t>可靠的办公收入，房客流失少。</t>
+  </si>
+  <si>
+    <t>ReduceMoney;20</t>
+  </si>
+  <si>
+    <t>租赁账本</t>
+  </si>
+  <si>
+    <t>把每个房间变成更清洁的收益线。</t>
+  </si>
+  <si>
+    <t>长期租约</t>
+  </si>
+  <si>
+    <t>在多个回合内锁定低风险收入。</t>
+  </si>
+  <si>
+    <t>AddMoney;20|AddTenantDurability;1</t>
+  </si>
+  <si>
+    <t>夜骑手</t>
+  </si>
+  <si>
+    <t>短期入住，高速节奏，容易变现。</t>
+  </si>
+  <si>
+    <t>清仓招牌</t>
+  </si>
+  <si>
+    <t>让繁忙房间持续转化为现金。</t>
+  </si>
+  <si>
+    <t>招聘电话</t>
+  </si>
+  <si>
+    <t>立即抽牌补充手牌。</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Tempo</t>
+  </si>
+  <si>
+    <t>搬迁令</t>
+  </si>
+  <si>
+    <t>让头号房客搬出，为下一步计划腾出房间。</t>
+  </si>
+  <si>
+    <t>MoveTenantToEmptyRoom|AddMoney;20</t>
+  </si>
+  <si>
+    <t>QuickTurnover|Control</t>
+  </si>
+  <si>
+    <t>万能工</t>
+  </si>
+  <si>
+    <t>保持房间硬件完好，照常交租。</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;1</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Core</t>
+  </si>
+  <si>
+    <t>额外书架</t>
+  </si>
+  <si>
+    <t>为堆满的房间增加一个房客位置。</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Engine</t>
+  </si>
+  <si>
+    <t>电源插座</t>
+  </si>
+  <si>
+    <t>温和升级让叠放设备保持高效。</t>
+  </si>
+  <si>
+    <t>AddMoney;10|AddEquipmentDurability;1</t>
+  </si>
+  <si>
+    <t>维修队</t>
+  </si>
+  <si>
+    <t>修复建筑并把维护费转化为小额收益。</t>
+  </si>
+  <si>
+    <t>AddEquipmentDurability;3|AddMoney;40</t>
+  </si>
+  <si>
+    <t>EquipmentStack|Bridge</t>
+  </si>
+  <si>
+    <t>开放屋标志</t>
+  </si>
+  <si>
+    <t>房屋越空，表现越好。</t>
+  </si>
+  <si>
+    <t>AddMoneyByEmptyRooms;15</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Support</t>
+  </si>
+  <si>
+    <t>空房条款</t>
+  </si>
+  <si>
+    <t>单位保持空房时付款更高。</t>
+  </si>
+  <si>
+    <t>AddMoneyByEmptyRooms;25</t>
+  </si>
+  <si>
+    <t>VacancyEconomy|Anchor</t>
+  </si>
+  <si>
+    <t>楼层规划师</t>
+  </si>
+  <si>
+    <t>每增加一个房间就赚一点。</t>
+  </si>
+  <si>
+    <t>AddMoneyByRoomCount;10</t>
+  </si>
+  <si>
+    <t>施工许可</t>
+  </si>
+  <si>
+    <t>增加一个房间并在手牌中替换自己。</t>
+  </si>
+  <si>
+    <t>AddRoom|DrawCard;1</t>
+  </si>
+  <si>
+    <t>Expansion|Bridge</t>
+  </si>
+  <si>
+    <t>夜间审计员</t>
+  </si>
+  <si>
+    <t>选中的房间满客时支付更多。</t>
+  </si>
+  <si>
+    <t>AddMoneyBySelectedRoomTenantCount;20</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Core</t>
+  </si>
+  <si>
+    <t>快速结算</t>
+  </si>
+  <si>
+    <t>为选中的房间触发一次安全的额外结算。</t>
+  </si>
+  <si>
+    <t>TriggerSelectedRoomSettle</t>
+  </si>
+  <si>
+    <t>BurstSettlement|Tempo</t>
+  </si>
+  <si>
     <t>工人</t>
   </si>
   <si>
     <t>勤快的工人，准时交租。</t>
   </si>
   <si>
-    <t>Card_Tenant</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
     <t>AddMoney;60</t>
   </si>
   <si>
-    <t>ReduceMoney;30</t>
-  </si>
-  <si>
-    <t>SteadyRent|Core</t>
-  </si>
-  <si>
-    <t>白领</t>
-  </si>
-  <si>
-    <t>工作稳定，房间整洁。</t>
-  </si>
-  <si>
-    <t>AddMoney;120</t>
-  </si>
-  <si>
-    <t>ReduceMoney;60</t>
-  </si>
-  <si>
-    <t>程序员</t>
-  </si>
-  <si>
-    <t>高薪但经常加班。</t>
-  </si>
-  <si>
-    <t>AddMoney;200</t>
-  </si>
-  <si>
-    <t>ReduceMoney;100</t>
-  </si>
-  <si>
-    <t>QuickTurnover|Payoff</t>
-  </si>
-  <si>
-    <t>高级教师</t>
-  </si>
-  <si>
-    <t>安静的老房客，长住不走。</t>
-  </si>
-  <si>
-    <t>AddMoney;50</t>
-  </si>
-  <si>
-    <t>ReduceMoney;25</t>
-  </si>
-  <si>
-    <t>SteadyRent|Anchor</t>
+    <t>0|1</t>
   </si>
   <si>
     <t>学生</t>
@@ -212,108 +629,18 @@
     <t>AddMoney;40</t>
   </si>
   <si>
-    <t>ReduceMoney;20</t>
-  </si>
-  <si>
     <t>VacancyEconomy|Starter</t>
   </si>
   <si>
-    <t>主播</t>
-  </si>
-  <si>
-    <t>高收入但经常搬家。</t>
-  </si>
-  <si>
-    <t>AddMoney;240</t>
-  </si>
-  <si>
-    <t>ReduceMoney;120</t>
-  </si>
-  <si>
-    <t>医生</t>
-  </si>
-  <si>
-    <t>定金高，长期承租。</t>
-  </si>
-  <si>
-    <t>AddMoney;160</t>
-  </si>
-  <si>
-    <t>ReduceMoney;80</t>
-  </si>
-  <si>
-    <t>厨师</t>
-  </si>
-  <si>
-    <t>稳定可靠的好房客。</t>
-  </si>
-  <si>
-    <t>AddMoney;100</t>
-  </si>
-  <si>
-    <t>ReduceMoney;50</t>
-  </si>
-  <si>
-    <t>EquipmentStack|Support</t>
-  </si>
-  <si>
-    <t>画家</t>
-  </si>
-  <si>
-    <t>需要时间适应新房间。</t>
-  </si>
-  <si>
-    <t>AddMoney;80</t>
-  </si>
-  <si>
-    <t>ReduceMoney;40</t>
-  </si>
-  <si>
-    <t>Expansion|Setup</t>
-  </si>
-  <si>
     <t>快递员</t>
   </si>
   <si>
     <t>来得快，去得也快。</t>
   </si>
   <si>
-    <t>AddMoney;70</t>
-  </si>
-  <si>
     <t>ReduceMoney;35</t>
   </si>
   <si>
-    <t>QuickTurnover|Bridge</t>
-  </si>
-  <si>
-    <t>空调</t>
-  </si>
-  <si>
-    <t>提升房间舒适度。</t>
-  </si>
-  <si>
-    <t>Card_Equipt</t>
-  </si>
-  <si>
-    <t>AddMoney;10</t>
-  </si>
-  <si>
-    <t>SteadyRent|Support</t>
-  </si>
-  <si>
-    <t>双层床</t>
-  </si>
-  <si>
-    <t>增加一个房客位置。</t>
-  </si>
-  <si>
-    <t>ExpandSlot;1</t>
-  </si>
-  <si>
-    <t>Expansion|Engine</t>
-  </si>
-  <si>
     <t>热水器</t>
   </si>
   <si>
@@ -323,96 +650,12 @@
     <t>AddMoney;5</t>
   </si>
   <si>
-    <t>WiFi路由器</t>
-  </si>
-  <si>
-    <t>生活必需品。</t>
-  </si>
-  <si>
-    <t>AddMoney;15</t>
-  </si>
-  <si>
-    <t>QuickTurnover|Support</t>
-  </si>
-  <si>
-    <t>洗衣机</t>
-  </si>
-  <si>
-    <t>洗衣便利性。</t>
-  </si>
-  <si>
-    <t>AddMoney;8</t>
-  </si>
-  <si>
     <t>租金奖励</t>
   </si>
   <si>
     <t>额外的租金收入。</t>
   </si>
   <si>
-    <t>Card_Event</t>
-  </si>
-  <si>
-    <t>PlayArea</t>
-  </si>
-  <si>
-    <t>BurstSettlement|Payoff</t>
-  </si>
-  <si>
-    <t>经纪人介绍</t>
-  </si>
-  <si>
-    <t>支付费用抽取2张牌。</t>
-  </si>
-  <si>
-    <t>DrawCard;2</t>
-  </si>
-  <si>
-    <t>续签</t>
-  </si>
-  <si>
-    <t>说服所有房客留下。</t>
-  </si>
-  <si>
-    <t>AddTenantDurability;3</t>
-  </si>
-  <si>
-    <t>维修</t>
-  </si>
-  <si>
-    <t>修复所有设备。</t>
-  </si>
-  <si>
-    <t>AddEquipmentDurability;3</t>
-  </si>
-  <si>
-    <t>应急贷款</t>
-  </si>
-  <si>
-    <t>银行紧急资金。</t>
-  </si>
-  <si>
-    <t>AddMoney;500</t>
-  </si>
-  <si>
-    <t>工会文员</t>
-  </si>
-  <si>
-    <t>可靠的办公收入，房客流失少。</t>
-  </si>
-  <si>
-    <t>夜班护士</t>
-  </si>
-  <si>
-    <t>长班次，稳定回报，难以驱赶。</t>
-  </si>
-  <si>
-    <t>租赁账本</t>
-  </si>
-  <si>
-    <t>把每个房间变成更清洁的收益线。</t>
-  </si>
-  <si>
     <t>催租单</t>
   </si>
   <si>
@@ -425,18 +668,6 @@
     <t>SteadyRent|Tempo</t>
   </si>
   <si>
-    <t>长期租约</t>
-  </si>
-  <si>
-    <t>在多个回合内锁定低风险收入。</t>
-  </si>
-  <si>
-    <t>Card_Contract</t>
-  </si>
-  <si>
-    <t>AddMoney;20|AddTenantDurability;1</t>
-  </si>
-  <si>
     <t>临时工</t>
   </si>
   <si>
@@ -446,93 +677,6 @@
     <t>QuickTurnover|Core</t>
   </si>
   <si>
-    <t>夜骑手</t>
-  </si>
-  <si>
-    <t>短期入住，高速节奏，容易变现。</t>
-  </si>
-  <si>
-    <t>清仓招牌</t>
-  </si>
-  <si>
-    <t>让繁忙房间持续转化为现金。</t>
-  </si>
-  <si>
-    <t>招聘电话</t>
-  </si>
-  <si>
-    <t>立即抽牌补充手牌。</t>
-  </si>
-  <si>
-    <t>QuickTurnover|Tempo</t>
-  </si>
-  <si>
-    <t>搬迁令</t>
-  </si>
-  <si>
-    <t>让头号房客搬出，为下一步计划腾出房间。</t>
-  </si>
-  <si>
-    <t>MoveTenantToEmptyRoom|AddMoney;20</t>
-  </si>
-  <si>
-    <t>QuickTurnover|Control</t>
-  </si>
-  <si>
-    <t>万能工</t>
-  </si>
-  <si>
-    <t>保持房间硬件完好，照常交租。</t>
-  </si>
-  <si>
-    <t>AddEquipmentDurability;1</t>
-  </si>
-  <si>
-    <t>EquipmentStack|Core</t>
-  </si>
-  <si>
-    <t>额外书架</t>
-  </si>
-  <si>
-    <t>为堆满的房间增加一个房客位置。</t>
-  </si>
-  <si>
-    <t>EquipmentStack|Engine</t>
-  </si>
-  <si>
-    <t>电源插座</t>
-  </si>
-  <si>
-    <t>温和升级让叠放设备保持高效。</t>
-  </si>
-  <si>
-    <t>AddMoney;10|AddEquipmentDurability;1</t>
-  </si>
-  <si>
-    <t>洗衣堆</t>
-  </si>
-  <si>
-    <t>提升房间舒适度，房客留存更久。</t>
-  </si>
-  <si>
-    <t>AddMoney;12|AddTenantDurabilityInSelectedRoom;1</t>
-  </si>
-  <si>
-    <t>EquipmentStack|Sustain</t>
-  </si>
-  <si>
-    <t>维修队</t>
-  </si>
-  <si>
-    <t>修复建筑并把维护费转化为小额收益。</t>
-  </si>
-  <si>
-    <t>AddEquipmentDurability;3|AddMoney;40</t>
-  </si>
-  <si>
-    <t>EquipmentStack|Bridge</t>
-  </si>
-  <si>
     <t>转租户</t>
   </si>
   <si>
@@ -545,18 +689,6 @@
     <t>VacancyEconomy|Core</t>
   </si>
   <si>
-    <t>开放屋标志</t>
-  </si>
-  <si>
-    <t>房屋越空，表现越好。</t>
-  </si>
-  <si>
-    <t>AddMoneyByEmptyRooms;15</t>
-  </si>
-  <si>
-    <t>VacancyEconomy|Support</t>
-  </si>
-  <si>
     <t>空房清单</t>
   </si>
   <si>
@@ -579,129 +711,6 @@
   </si>
   <si>
     <t>VacancyEconomy|Bridge</t>
-  </si>
-  <si>
-    <t>空房条款</t>
-  </si>
-  <si>
-    <t>单位保持空房时付款更高。</t>
-  </si>
-  <si>
-    <t>AddMoneyByEmptyRooms;25</t>
-  </si>
-  <si>
-    <t>VacancyEconomy|Anchor</t>
-  </si>
-  <si>
-    <t>楼层规划师</t>
-  </si>
-  <si>
-    <t>每增加一个房间就赚一点。</t>
-  </si>
-  <si>
-    <t>AddMoneyByRoomCount;10</t>
-  </si>
-  <si>
-    <t>Expansion|Core</t>
-  </si>
-  <si>
-    <t>装修负责人</t>
-  </si>
-  <si>
-    <t>建筑有更多房间在用时获得奖励。</t>
-  </si>
-  <si>
-    <t>AddMoneyByRoomCount;12</t>
-  </si>
-  <si>
-    <t>隔断墙</t>
-  </si>
-  <si>
-    <t>纯容量增长，无额外条件。</t>
-  </si>
-  <si>
-    <t>ExpandSlot;2</t>
-  </si>
-  <si>
-    <t>施工许可</t>
-  </si>
-  <si>
-    <t>增加一个房间并在手牌中替换自己。</t>
-  </si>
-  <si>
-    <t>AddRoom|DrawCard;1</t>
-  </si>
-  <si>
-    <t>Expansion|Bridge</t>
-  </si>
-  <si>
-    <t>蓝图交易</t>
-  </si>
-  <si>
-    <t>随着地产增长而变得更好的可扩展合约。</t>
-  </si>
-  <si>
-    <t>AddMoneyByRoomCount;20|DrawCard;1</t>
-  </si>
-  <si>
-    <t>Expansion|Anchor</t>
-  </si>
-  <si>
-    <t>夜间审计员</t>
-  </si>
-  <si>
-    <t>选中的房间满客时支付更多。</t>
-  </si>
-  <si>
-    <t>AddMoneyBySelectedRoomTenantCount;20</t>
-  </si>
-  <si>
-    <t>BurstSettlement|Core</t>
-  </si>
-  <si>
-    <t>闪电经纪人</t>
-  </si>
-  <si>
-    <t>短期高薪房客，留下增值残余。</t>
-  </si>
-  <si>
-    <t>AddMoneyBySelectedRoomTenantCount;25</t>
-  </si>
-  <si>
-    <t>涡轮计价表</t>
-  </si>
-  <si>
-    <t>把房间密度转化为每次结算的额外冲刺。</t>
-  </si>
-  <si>
-    <t>AddMoneyBySelectedRoomTenantCount;10|AddMoney;15</t>
-  </si>
-  <si>
-    <t>BurstSettlement|Support</t>
-  </si>
-  <si>
-    <t>快速结算</t>
-  </si>
-  <si>
-    <t>为选中的房间触发一次安全的额外结算。</t>
-  </si>
-  <si>
-    <t>TriggerSelectedRoomSettle</t>
-  </si>
-  <si>
-    <t>BurstSettlement|Tempo</t>
-  </si>
-  <si>
-    <t>最终对账</t>
-  </si>
-  <si>
-    <t>短期合约推动最后的现金和牌张突发。</t>
-  </si>
-  <si>
-    <t>AddMoney;35|DrawCard;1</t>
-  </si>
-  <si>
-    <t>BurstSettlement|Anchor</t>
   </si>
 </sst>
 </file>
@@ -2116,7 +2125,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -2128,25 +2137,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
         <v>39</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I4" t="s">
         <v>40</v>
       </c>
-      <c r="J4">
-        <v>0</v>
+      <c r="J4" s="3">
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" t="s">
         <v>39</v>
@@ -2163,72 +2172,72 @@
       <c r="P4" t="s">
         <v>43</v>
       </c>
-      <c r="Q4" s="3">
-        <v>0</v>
+      <c r="Q4" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
         <v>38</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
       </c>
       <c r="G5">
+        <v>150</v>
+      </c>
+      <c r="H5">
         <v>120</v>
-      </c>
-      <c r="H5">
-        <v>60</v>
       </c>
       <c r="I5" t="s">
         <v>40</v>
       </c>
-      <c r="J5">
-        <v>0</v>
+      <c r="J5" s="3">
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L5" t="s">
         <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5" t="s">
         <v>39</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P5" t="s">
         <v>43</v>
       </c>
-      <c r="Q5" s="3">
-        <v>0</v>
+      <c r="Q5" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
@@ -2240,63 +2249,63 @@
         <v>39</v>
       </c>
       <c r="G6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
         <v>40</v>
       </c>
-      <c r="J6">
-        <v>0</v>
+      <c r="J6" s="3">
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L6" t="s">
         <v>39</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N6" t="s">
         <v>39</v>
       </c>
       <c r="O6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P6" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7">
-        <v>1004</v>
+        <v>2002</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I7" t="s">
         <v>40</v>
@@ -2311,83 +2320,83 @@
         <v>39</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N7" t="s">
         <v>39</v>
       </c>
       <c r="O7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P7" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8">
-        <v>1005</v>
+        <v>3005</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="s">
         <v>39</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="s">
         <v>39</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N8" t="s">
         <v>39</v>
       </c>
       <c r="O8" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P8" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
@@ -2399,51 +2408,51 @@
         <v>39</v>
       </c>
       <c r="G9">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
         <v>40</v>
       </c>
-      <c r="J9">
-        <v>0</v>
+      <c r="J9" s="3">
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L9" t="s">
         <v>39</v>
       </c>
       <c r="M9" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="N9" t="s">
         <v>39</v>
       </c>
       <c r="O9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10">
-        <v>1007</v>
+        <v>2010</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -2452,10 +2461,10 @@
         <v>39</v>
       </c>
       <c r="G10">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="H10">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>40</v>
@@ -2464,83 +2473,83 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L10" t="s">
         <v>39</v>
       </c>
       <c r="M10" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="P10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H11">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
         <v>40</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11" t="s">
         <v>39</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="P11" t="s">
         <v>75</v>
       </c>
-      <c r="Q11" s="3">
-        <v>0</v>
+      <c r="Q11" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12">
-        <v>1009</v>
+        <v>2012</v>
       </c>
       <c r="B12" t="s">
         <v>76</v>
@@ -2549,28 +2558,28 @@
         <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I12" t="s">
         <v>40</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L12" t="s">
         <v>39</v>
@@ -2582,83 +2591,83 @@
         <v>39</v>
       </c>
       <c r="O12" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="P12" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13">
-        <v>1010</v>
+        <v>4003</v>
       </c>
       <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
         <v>81</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13">
+        <v>140</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" t="s">
         <v>82</v>
       </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13">
-        <v>40</v>
-      </c>
-      <c r="H13">
-        <v>35</v>
-      </c>
-      <c r="I13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>3</v>
-      </c>
-      <c r="L13" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="O13" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" t="s">
         <v>83</v>
       </c>
-      <c r="N13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" t="s">
-        <v>84</v>
-      </c>
-      <c r="P13" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0</v>
+      <c r="Q13" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14">
-        <v>2001</v>
+        <v>1020</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
@@ -2667,16 +2676,16 @@
         <v>80</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
         <v>40</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14" t="s">
         <v>39</v>
@@ -2685,30 +2694,30 @@
         <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O14" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="P14" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2717,7 +2726,7 @@
         <v>39</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2729,92 +2738,92 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" t="s">
         <v>39</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="O15" t="s">
         <v>39</v>
       </c>
       <c r="P15" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+        <v>91</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16">
-        <v>2003</v>
+        <v>4004</v>
       </c>
       <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16">
+        <v>130</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O16" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" t="s">
         <v>95</v>
       </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16">
-        <v>60</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="s">
-        <v>40</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>8</v>
-      </c>
-      <c r="L16" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" t="s">
-        <v>39</v>
-      </c>
-      <c r="N16" t="s">
-        <v>97</v>
-      </c>
-      <c r="O16" t="s">
-        <v>39</v>
-      </c>
-      <c r="P16" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>0</v>
+      <c r="Q16" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17">
-        <v>2004</v>
+        <v>1002</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2823,51 +2832,51 @@
         <v>39</v>
       </c>
       <c r="G17">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I17" t="s">
         <v>40</v>
       </c>
-      <c r="J17">
-        <v>0</v>
+      <c r="J17" s="3">
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L17" t="s">
         <v>39</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="N17" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="O17" t="s">
-        <v>39</v>
-      </c>
-      <c r="P17" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18">
-        <v>2005</v>
+        <v>1004</v>
       </c>
       <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
         <v>102</v>
       </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2876,104 +2885,104 @@
         <v>39</v>
       </c>
       <c r="G18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
         <v>40</v>
       </c>
-      <c r="J18">
-        <v>0</v>
+      <c r="J18" s="3">
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
         <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="N18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O18" t="s">
         <v>104</v>
       </c>
-      <c r="O18" t="s">
-        <v>39</v>
-      </c>
       <c r="P18" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19">
-        <v>3001</v>
+        <v>1008</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="3">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>6</v>
+      </c>
+      <c r="L19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19" t="s">
         <v>108</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" t="s">
-        <v>50</v>
-      </c>
       <c r="N19" t="s">
         <v>39</v>
       </c>
       <c r="O19" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20">
-        <v>3002</v>
+        <v>1009</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2982,51 +2991,51 @@
         <v>39</v>
       </c>
       <c r="G20">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" t="s">
         <v>39</v>
       </c>
       <c r="M20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N20" t="s">
         <v>39</v>
       </c>
       <c r="O20" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="P20" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21">
-        <v>3003</v>
+        <v>2001</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -3041,45 +3050,45 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" t="s">
         <v>39</v>
       </c>
       <c r="M21" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="N21" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="O21" t="s">
         <v>39</v>
       </c>
       <c r="P21" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22">
-        <v>3004</v>
+        <v>2004</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -3088,104 +3097,104 @@
         <v>39</v>
       </c>
       <c r="G22">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22" t="s">
         <v>39</v>
       </c>
       <c r="M22" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="N22" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="O22" t="s">
         <v>39</v>
       </c>
       <c r="P22" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23">
-        <v>3005</v>
+        <v>2005</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L23" t="s">
         <v>39</v>
       </c>
       <c r="M23" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="N23" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="O23" t="s">
         <v>39</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24">
-        <v>1011</v>
+        <v>3002</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -3194,104 +3203,104 @@
         <v>39</v>
       </c>
       <c r="G24">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H24">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>39</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="N24" t="s">
         <v>39</v>
       </c>
       <c r="O24" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25">
-        <v>1012</v>
+        <v>3003</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
       </c>
       <c r="G25">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="H25">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L25" t="s">
         <v>39</v>
       </c>
       <c r="M25" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="N25" t="s">
         <v>39</v>
       </c>
       <c r="O25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P25" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26">
-        <v>2006</v>
+        <v>3004</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -3300,104 +3309,104 @@
         <v>39</v>
       </c>
       <c r="G26">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L26" t="s">
         <v>39</v>
       </c>
       <c r="M26" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="N26" t="s">
+        <v>39</v>
+      </c>
+      <c r="O26" t="s">
+        <v>39</v>
+      </c>
+      <c r="P26" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q26" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="O26" t="s">
-        <v>39</v>
-      </c>
-      <c r="P26" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27">
-        <v>3006</v>
+        <v>1011</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
       </c>
       <c r="G27">
+        <v>70</v>
+      </c>
+      <c r="H27">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
         <v>40</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>108</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
+      <c r="J27" s="3">
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L27" t="s">
         <v>39</v>
       </c>
       <c r="M27" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="N27" t="s">
         <v>39</v>
       </c>
       <c r="O27" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="P27" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28">
-        <v>4001</v>
+        <v>2006</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -3406,19 +3415,19 @@
         <v>39</v>
       </c>
       <c r="G28">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28" t="s">
         <v>39</v>
@@ -3427,45 +3436,45 @@
         <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="O28" t="s">
         <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29">
-        <v>1013</v>
+        <v>4001</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
         <v>39</v>
       </c>
       <c r="G29">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="H29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3480,16 +3489,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="O29" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P29" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -3497,10 +3506,10 @@
         <v>1014</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
         <v>38</v>
@@ -3520,8 +3529,8 @@
       <c r="I30" t="s">
         <v>40</v>
       </c>
-      <c r="J30">
-        <v>0</v>
+      <c r="J30" s="3">
+        <v>2</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -3536,13 +3545,13 @@
         <v>39</v>
       </c>
       <c r="O30" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P30" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q30" s="3">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -3550,13 +3559,13 @@
         <v>2007</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -3586,16 +3595,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="O31" t="s">
         <v>39</v>
       </c>
       <c r="P31" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q31" s="3">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -3603,13 +3612,13 @@
         <v>3007</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -3624,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -3636,7 +3645,7 @@
         <v>39</v>
       </c>
       <c r="M32" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="N32" t="s">
         <v>39</v>
@@ -3645,10 +3654,10 @@
         <v>39</v>
       </c>
       <c r="P32" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -3656,13 +3665,13 @@
         <v>3008</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -3689,7 +3698,7 @@
         <v>39</v>
       </c>
       <c r="M33" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N33" t="s">
         <v>39</v>
@@ -3698,10 +3707,10 @@
         <v>39</v>
       </c>
       <c r="P33" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>0</v>
+        <v>155</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -3709,10 +3718,10 @@
         <v>1015</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
@@ -3733,7 +3742,7 @@
         <v>40</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34">
         <v>5</v>
@@ -3745,16 +3754,16 @@
         <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="O34" t="s">
         <v>39</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -3762,13 +3771,13 @@
         <v>2008</v>
       </c>
       <c r="B35" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3795,7 +3804,7 @@
         <v>39</v>
       </c>
       <c r="M35" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="N35" t="s">
         <v>39</v>
@@ -3804,10 +3813,10 @@
         <v>39</v>
       </c>
       <c r="P35" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -3815,13 +3824,13 @@
         <v>2009</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D36" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3851,83 +3860,83 @@
         <v>39</v>
       </c>
       <c r="N36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O36" t="s">
         <v>39</v>
       </c>
       <c r="P36" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q36" s="3">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37">
-        <v>2010</v>
+        <v>3009</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
       </c>
       <c r="G37">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L37" t="s">
         <v>39</v>
       </c>
       <c r="M37" t="s">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="N37" t="s">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="O37" t="s">
         <v>39</v>
       </c>
       <c r="P37" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q37" s="3">
-        <v>0</v>
+        <v>169</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38">
-        <v>3009</v>
+        <v>2011</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3936,66 +3945,66 @@
         <v>39</v>
       </c>
       <c r="G38">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" t="s">
         <v>39</v>
       </c>
       <c r="M38" t="s">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="O38" t="s">
         <v>39</v>
       </c>
       <c r="P38" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q38" s="3">
-        <v>0</v>
+        <v>173</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39">
-        <v>1016</v>
+        <v>4002</v>
       </c>
       <c r="B39" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="s">
         <v>39</v>
       </c>
       <c r="G39">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4010,30 +4019,30 @@
         <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="O39" t="s">
         <v>39</v>
       </c>
       <c r="P39" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q39" s="3">
-        <v>0</v>
+        <v>177</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40">
-        <v>2011</v>
+        <v>1017</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C40" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -4042,19 +4051,19 @@
         <v>39</v>
       </c>
       <c r="G40">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
         <v>40</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L40" t="s">
         <v>39</v>
@@ -4063,45 +4072,45 @@
         <v>39</v>
       </c>
       <c r="N40" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="O40" t="s">
         <v>39</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41">
-        <v>3010</v>
+        <v>3012</v>
       </c>
       <c r="B41" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -4113,7 +4122,7 @@
         <v>39</v>
       </c>
       <c r="M41" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N41" t="s">
         <v>39</v>
@@ -4122,77 +4131,77 @@
         <v>39</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>0</v>
+        <v>184</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42">
-        <v>3011</v>
+        <v>1019</v>
       </c>
       <c r="B42" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C42" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" t="s">
         <v>39</v>
       </c>
       <c r="M42" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>39</v>
+        <v>187</v>
       </c>
       <c r="O42" t="s">
         <v>39</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+        <v>188</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43">
-        <v>4002</v>
+        <v>3013</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -4201,69 +4210,69 @@
         <v>39</v>
       </c>
       <c r="G43">
+        <v>70</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="s">
+        <v>40</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
+        <v>39</v>
+      </c>
+      <c r="M43" t="s">
+        <v>191</v>
+      </c>
+      <c r="N43" t="s">
+        <v>39</v>
+      </c>
+      <c r="O43" t="s">
+        <v>39</v>
+      </c>
+      <c r="P43" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q43" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43" t="s">
-        <v>108</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>4</v>
-      </c>
-      <c r="L43" t="s">
-        <v>39</v>
-      </c>
-      <c r="M43" t="s">
-        <v>39</v>
-      </c>
-      <c r="N43" t="s">
-        <v>186</v>
-      </c>
-      <c r="O43" t="s">
-        <v>39</v>
-      </c>
-      <c r="P43" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D44" t="s">
         <v>38</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="s">
         <v>39</v>
       </c>
       <c r="G44">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H44">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I44" t="s">
         <v>40</v>
       </c>
-      <c r="J44">
-        <v>0</v>
+      <c r="J44" s="3">
+        <v>2</v>
       </c>
       <c r="K44">
         <v>5</v>
@@ -4272,307 +4281,307 @@
         <v>39</v>
       </c>
       <c r="M44" t="s">
-        <v>39</v>
+        <v>195</v>
       </c>
       <c r="N44" t="s">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="O44" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="P44" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C45" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D45" t="s">
         <v>38</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
       <c r="G45">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H45">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
         <v>40</v>
       </c>
-      <c r="J45">
-        <v>0</v>
+      <c r="J45" s="3">
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L45" t="s">
         <v>39</v>
       </c>
       <c r="M45" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="N45" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="O45" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46">
-        <v>2012</v>
+        <v>1010</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
       </c>
       <c r="G46">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
         <v>40</v>
       </c>
-      <c r="J46">
-        <v>0</v>
+      <c r="J46" s="3">
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L46" t="s">
         <v>39</v>
       </c>
       <c r="M46" t="s">
-        <v>197</v>
+        <v>87</v>
       </c>
       <c r="N46" t="s">
         <v>39</v>
       </c>
       <c r="O46" t="s">
-        <v>39</v>
+        <v>203</v>
       </c>
       <c r="P46" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47">
-        <v>3012</v>
+        <v>2003</v>
       </c>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C47" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="s">
         <v>39</v>
       </c>
       <c r="G47">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L47" t="s">
         <v>39</v>
       </c>
       <c r="M47" t="s">
-        <v>200</v>
+        <v>39</v>
       </c>
       <c r="N47" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="O47" t="s">
         <v>39</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48">
-        <v>4003</v>
+        <v>3001</v>
       </c>
       <c r="B48" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D48" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="s">
         <v>39</v>
       </c>
       <c r="G48">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L48" t="s">
         <v>39</v>
       </c>
       <c r="M48" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N48" t="s">
-        <v>204</v>
+        <v>39</v>
       </c>
       <c r="O48" t="s">
         <v>39</v>
       </c>
       <c r="P48" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49">
-        <v>1019</v>
+        <v>3006</v>
       </c>
       <c r="B49" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C49" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="s">
         <v>39</v>
       </c>
       <c r="G49">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H49">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L49" t="s">
         <v>39</v>
       </c>
       <c r="M49" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="N49" t="s">
-        <v>208</v>
+        <v>39</v>
       </c>
       <c r="O49" t="s">
         <v>39</v>
       </c>
       <c r="P49" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+        <v>212</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C50" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D50" t="s">
         <v>38</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
       </c>
       <c r="G50">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H50">
         <v>25</v>
@@ -4580,11 +4589,11 @@
       <c r="I50" t="s">
         <v>40</v>
       </c>
-      <c r="J50">
-        <v>0</v>
+      <c r="J50" s="3">
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" t="s">
         <v>39</v>
@@ -4593,48 +4602,48 @@
         <v>39</v>
       </c>
       <c r="N50" t="s">
-        <v>212</v>
+        <v>39</v>
       </c>
       <c r="O50" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="P50" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q50" s="3">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51">
-        <v>2013</v>
+        <v>1016</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D51" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
       </c>
       <c r="G51">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
         <v>40</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51">
         <v>4</v>
@@ -4646,39 +4655,39 @@
         <v>39</v>
       </c>
       <c r="N51" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O51" t="s">
         <v>39</v>
       </c>
       <c r="P51" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q51" s="3">
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="B52" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C52" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="s">
         <v>39</v>
       </c>
       <c r="G52">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -4696,7 +4705,7 @@
         <v>39</v>
       </c>
       <c r="M52" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N52" t="s">
         <v>39</v>
@@ -4705,66 +4714,69 @@
         <v>39</v>
       </c>
       <c r="P52" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+        <v>223</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53">
-        <v>4004</v>
+        <v>3011</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C53" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="s">
         <v>39</v>
       </c>
       <c r="G53">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" t="s">
         <v>39</v>
       </c>
       <c r="M53" t="s">
-        <v>39</v>
+        <v>226</v>
       </c>
       <c r="N53" t="s">
-        <v>223</v>
+        <v>39</v>
       </c>
       <c r="O53" t="s">
         <v>39</v>
       </c>
       <c r="P53" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q53" s="3">
-        <v>0</v>
+        <v>227</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:Q53">
+    <sortCondition ref="E4" descending="1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
